--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B300F08-0B99-4218-9B40-94FD8E5A3378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F764BD9E-C0C2-4BC7-AE62-E1A9AF29229E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,16 +561,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4022299883508069</v>
+        <v>1.4002904162633107</v>
       </c>
       <c r="C2" s="3">
-        <v>1.4132687390660745</v>
+        <v>1.4125986193293885</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32579700715679893</v>
+        <v>0.32557650890371381</v>
       </c>
       <c r="E2" s="4">
-        <v>0.12822238326948959</v>
+        <v>0.12716926115787988</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -578,16 +578,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3594066082265677</v>
+        <v>1.3591756624141313</v>
       </c>
       <c r="C3" s="3">
-        <v>1.3646732429099877</v>
+        <v>1.3683473389355745</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17644259369422963</v>
+        <v>0.17557865717075413</v>
       </c>
       <c r="E3" s="4">
-        <v>0.17409037243747988</v>
+        <v>0.16958814308108877</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -595,16 +595,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3269736842105262</v>
+        <v>1.3247191011235955</v>
       </c>
       <c r="C4" s="3">
-        <v>1.3190447030006125</v>
+        <v>1.3266591991038925</v>
       </c>
       <c r="D4" s="4">
-        <v>0.21919388564424255</v>
+        <v>0.21491651717952256</v>
       </c>
       <c r="E4" s="4">
-        <v>0.20724665270639001</v>
+        <v>0.2066550925925926</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -612,16 +612,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2967256457189344</v>
+        <v>1.2992642672499504</v>
       </c>
       <c r="C5" s="3">
-        <v>1.3368037480478916</v>
+        <v>1.3382928739232578</v>
       </c>
       <c r="D5" s="4">
-        <v>8.4057029540481401E-2</v>
+        <v>8.3771988272921108E-2</v>
       </c>
       <c r="E5" s="4">
-        <v>9.8249143324752375E-2</v>
+        <v>9.9015274870124834E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -629,16 +629,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2500462534690102</v>
+        <v>1.2486422881969588</v>
       </c>
       <c r="C6" s="3">
-        <v>1.250354432491035</v>
+        <v>1.2541574910775306</v>
       </c>
       <c r="D6" s="4">
-        <v>0.18077225371661734</v>
+        <v>0.18475225338216358</v>
       </c>
       <c r="E6" s="4">
-        <v>0.13893909899888765</v>
+        <v>0.13839234107842829</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -646,16 +646,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2312760521715744</v>
+        <v>1.2291584871090173</v>
       </c>
       <c r="C7" s="3">
-        <v>1.2246970994982256</v>
+        <v>1.2230263890435364</v>
       </c>
       <c r="D7" s="4">
-        <v>9.8551608072830393E-2</v>
+        <v>9.8377752027809962E-2</v>
       </c>
       <c r="E7" s="4">
-        <v>0.10209538565341797</v>
+        <v>0.10156515052133988</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -663,50 +663,50 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2266163793103448</v>
+        <v>1.2270958241295888</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2016724053123464</v>
+        <v>1.198581560283688</v>
       </c>
       <c r="D8" s="4">
-        <v>0.10021814726020001</v>
+        <v>9.9953739722858884E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>9.078223204617257E-2</v>
+        <v>8.9737470167064445E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2245762711864407</v>
+        <v>1.223475808201345</v>
       </c>
       <c r="C9" s="3">
-        <v>1.2763180789977377</v>
+        <v>1.2364970197157266</v>
       </c>
       <c r="D9" s="4">
-        <v>6.9854029381065885E-2</v>
+        <v>0.11214111922141119</v>
       </c>
       <c r="E9" s="4">
-        <v>7.4241054127373723E-2</v>
+        <v>0.10959138142423572</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2244920617297657</v>
+        <v>1.2230371009490941</v>
       </c>
       <c r="C10" s="3">
-        <v>1.2383614555804026</v>
+        <v>1.3143807412100095</v>
       </c>
       <c r="D10" s="4">
-        <v>0.11242869446906245</v>
+        <v>6.9952017382382228E-2</v>
       </c>
       <c r="E10" s="4">
-        <v>0.1095618860948393</v>
+        <v>7.4310328594294317E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -714,16 +714,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2102747909199523</v>
+        <v>1.2071925754060324</v>
       </c>
       <c r="C11" s="3">
-        <v>1.2127823904228616</v>
+        <v>1.2062543921293043</v>
       </c>
       <c r="D11" s="4">
-        <v>9.4051284356248738E-2</v>
+        <v>9.4252974107767673E-2</v>
       </c>
       <c r="E11" s="4">
-        <v>9.5866575347537161E-2</v>
+        <v>9.5168032101655239E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -731,118 +731,118 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2068074105988797</v>
+        <v>1.2062761506276152</v>
       </c>
       <c r="C12" s="3">
-        <v>1.3470031545741326</v>
+        <v>1.3296387520525452</v>
       </c>
       <c r="D12" s="4">
-        <v>8.9009050467863171E-2</v>
+        <v>8.9079388743943347E-2</v>
       </c>
       <c r="E12" s="4">
-        <v>8.6934378060724779E-2</v>
+        <v>8.6795410817359087E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>1.1993658343242173</v>
+        <v>1.200087374399301</v>
       </c>
       <c r="C13" s="3">
-        <v>1.2116212338593972</v>
+        <v>1.2132674396502567</v>
       </c>
       <c r="D13" s="4">
-        <v>9.9609143669311853E-2</v>
+        <v>8.1591188579372295E-2</v>
       </c>
       <c r="E13" s="4">
-        <v>0.10471361502347418</v>
+        <v>8.2431098506807896E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1969781757134861</v>
+        <v>1.1996507566938301</v>
       </c>
       <c r="C14" s="3">
-        <v>1.2359897172236505</v>
+        <v>1.2106203312763884</v>
       </c>
       <c r="D14" s="4">
-        <v>8.5204787107233115E-2</v>
+        <v>9.8966934214063523E-2</v>
       </c>
       <c r="E14" s="4">
-        <v>8.3397650287282396E-2</v>
+        <v>0.10424743105754093</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1930761622156281</v>
+        <v>1.1963023382272975</v>
       </c>
       <c r="C15" s="3">
-        <v>1.1883519206939281</v>
+        <v>1.2410423452768728</v>
       </c>
       <c r="D15" s="4">
-        <v>0.11368236405343408</v>
+        <v>8.5190160744892759E-2</v>
       </c>
       <c r="E15" s="4">
-        <v>0.10099402867665463</v>
+        <v>8.3184950065804758E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1929176623940909</v>
+        <v>1.1930232558139535</v>
       </c>
       <c r="C16" s="3">
-        <v>1.201725012683917</v>
+        <v>1.1877350776778415</v>
       </c>
       <c r="D16" s="4">
-        <v>0.12567746515405934</v>
+        <v>0.11319264686526566</v>
       </c>
       <c r="E16" s="4">
-        <v>0.12195423777054536</v>
+        <v>0.10043689639314106</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1910512463229603</v>
+        <v>1.191932059447983</v>
       </c>
       <c r="C17" s="3">
-        <v>1.2233621574087645</v>
+        <v>1.2050975340449024</v>
       </c>
       <c r="D17" s="4">
-        <v>8.960628173469104E-2</v>
+        <v>0.12514281159497304</v>
       </c>
       <c r="E17" s="4">
-        <v>8.4055042932994956E-2</v>
+        <v>0.12177849491282328</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1899641577060933</v>
+        <v>1.189806412583182</v>
       </c>
       <c r="C18" s="3">
-        <v>1.2135922330097089</v>
+        <v>1.2181600638128158</v>
       </c>
       <c r="D18" s="4">
-        <v>8.229481601651796E-2</v>
+        <v>9.0336507589523593E-2</v>
       </c>
       <c r="E18" s="4">
-        <v>8.3290849960446514E-2</v>
+        <v>8.3969636079482032E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -850,16 +850,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.180901627538528</v>
+        <v>1.1806024774774775</v>
       </c>
       <c r="C19" s="3">
-        <v>1.1988727858293076</v>
+        <v>1.1951189749847468</v>
       </c>
       <c r="D19" s="4">
-        <v>8.8217729946761872E-2</v>
+        <v>8.7643110935649429E-2</v>
       </c>
       <c r="E19" s="4">
-        <v>8.7093720416535181E-2</v>
+        <v>8.647707486941382E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -867,16 +867,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.174892041949414</v>
+        <v>1.173496859108585</v>
       </c>
       <c r="C20" s="3">
-        <v>1.2026419336706016</v>
+        <v>1.19892610585528</v>
       </c>
       <c r="D20" s="4">
-        <v>8.850910480766605E-2</v>
+        <v>8.854456363395577E-2</v>
       </c>
       <c r="E20" s="4">
-        <v>9.2934569674807371E-2</v>
+        <v>9.2772256090329006E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -884,16 +884,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2357381173767981</v>
+        <v>1.2353610612230381</v>
       </c>
       <c r="C21" s="7">
-        <v>1.2502607578248208</v>
+        <v>1.2514612346390315</v>
       </c>
       <c r="D21" s="8">
-        <v>0.11022365661841321</v>
+        <v>0.1100828895559551</v>
       </c>
       <c r="E21" s="8">
-        <v>0.10469837941728913</v>
+        <v>0.10421525499788266</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F764BD9E-C0C2-4BC7-AE62-E1A9AF29229E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AABEEAD-01A5-4903-8D41-AF9280D48E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,6 +132,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -561,13 +562,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4002904162633107</v>
+        <v>1.4036752522970328</v>
       </c>
       <c r="C2" s="3">
         <v>1.4125986193293885</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32557650890371381</v>
+        <v>0.32502692646626846</v>
       </c>
       <c r="E2" s="4">
         <v>0.12716926115787988</v>
@@ -578,13 +579,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3591756624141313</v>
+        <v>1.3620370370370372</v>
       </c>
       <c r="C3" s="3">
         <v>1.3683473389355745</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17557865717075413</v>
+        <v>0.1735404392072844</v>
       </c>
       <c r="E3" s="4">
         <v>0.16958814308108877</v>
@@ -595,13 +596,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3247191011235955</v>
+        <v>1.3247992728374489</v>
       </c>
       <c r="C4" s="3">
         <v>1.3266591991038925</v>
       </c>
       <c r="D4" s="4">
-        <v>0.21491651717952256</v>
+        <v>0.21293548387096775</v>
       </c>
       <c r="E4" s="4">
         <v>0.2066550925925926</v>
@@ -612,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2992642672499504</v>
+        <v>1.2977213298468435</v>
       </c>
       <c r="C5" s="3">
         <v>1.3382928739232578</v>
       </c>
       <c r="D5" s="4">
-        <v>8.3771988272921108E-2</v>
+        <v>8.3309992842249395E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.9015274870124834E-2</v>
@@ -629,13 +630,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2486422881969588</v>
+        <v>1.2475679302247569</v>
       </c>
       <c r="C6" s="3">
         <v>1.2541574910775306</v>
       </c>
       <c r="D6" s="4">
-        <v>0.18475225338216358</v>
+        <v>0.19940132778140102</v>
       </c>
       <c r="E6" s="4">
         <v>0.13839234107842829</v>
@@ -646,13 +647,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2291584871090173</v>
+        <v>1.2289702461124035</v>
       </c>
       <c r="C7" s="3">
         <v>1.2230263890435364</v>
       </c>
       <c r="D7" s="4">
-        <v>9.8377752027809962E-2</v>
+        <v>9.7879888301633522E-2</v>
       </c>
       <c r="E7" s="4">
         <v>0.10156515052133988</v>
@@ -663,13 +664,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2270958241295888</v>
+        <v>1.2263596276335129</v>
       </c>
       <c r="C8" s="3">
         <v>1.198581560283688</v>
       </c>
       <c r="D8" s="4">
-        <v>9.9953739722858884E-2</v>
+        <v>9.9659176359144133E-2</v>
       </c>
       <c r="E8" s="4">
         <v>8.9737470167064445E-2</v>
@@ -677,36 +678,36 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1.223475808201345</v>
+        <v>1.2254604331107064</v>
       </c>
       <c r="C9" s="3">
-        <v>1.2364970197157266</v>
+        <v>1.3143807412100095</v>
       </c>
       <c r="D9" s="4">
-        <v>0.11214111922141119</v>
+        <v>6.9682823980707118E-2</v>
       </c>
       <c r="E9" s="4">
-        <v>0.10959138142423572</v>
+        <v>7.4310328594294317E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2230371009490941</v>
+        <v>1.22349251315257</v>
       </c>
       <c r="C10" s="3">
-        <v>1.3143807412100095</v>
+        <v>1.2364970197157266</v>
       </c>
       <c r="D10" s="4">
-        <v>6.9952017382382228E-2</v>
+        <v>0.11138532968209428</v>
       </c>
       <c r="E10" s="4">
-        <v>7.4310328594294317E-2</v>
+        <v>0.10959138142423572</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -714,13 +715,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2071925754060324</v>
+        <v>1.2088840736728061</v>
       </c>
       <c r="C11" s="3">
         <v>1.2062543921293043</v>
       </c>
       <c r="D11" s="4">
-        <v>9.4252974107767673E-2</v>
+        <v>9.3781751676488515E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5168032101655239E-2</v>
@@ -731,13 +732,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2062761506276152</v>
+        <v>1.2041373926619829</v>
       </c>
       <c r="C12" s="3">
         <v>1.3296387520525452</v>
       </c>
       <c r="D12" s="4">
-        <v>8.9079388743943347E-2</v>
+        <v>8.843936621906176E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6795410817359087E-2</v>
@@ -748,13 +749,13 @@
         <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>1.200087374399301</v>
+        <v>1.1978021978021978</v>
       </c>
       <c r="C13" s="3">
         <v>1.2132674396502567</v>
       </c>
       <c r="D13" s="4">
-        <v>8.1591188579372295E-2</v>
+        <v>8.1564227264428107E-2</v>
       </c>
       <c r="E13" s="4">
         <v>8.2431098506807896E-2</v>
@@ -765,13 +766,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1996507566938301</v>
+        <v>1.1977289113193945</v>
       </c>
       <c r="C14" s="3">
         <v>1.2106203312763884</v>
       </c>
       <c r="D14" s="4">
-        <v>9.8966934214063523E-2</v>
+        <v>9.8657419756379483E-2</v>
       </c>
       <c r="E14" s="4">
         <v>0.10424743105754093</v>
@@ -782,13 +783,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1963023382272975</v>
+        <v>1.1961577350859456</v>
       </c>
       <c r="C15" s="3">
         <v>1.2410423452768728</v>
       </c>
       <c r="D15" s="4">
-        <v>8.5190160744892759E-2</v>
+        <v>8.4998495982123667E-2</v>
       </c>
       <c r="E15" s="4">
         <v>8.3184950065804758E-2</v>
@@ -799,13 +800,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1930232558139535</v>
+        <v>1.1922305307313517</v>
       </c>
       <c r="C16" s="3">
         <v>1.1877350776778415</v>
       </c>
       <c r="D16" s="4">
-        <v>0.11319264686526566</v>
+        <v>0.11219791687982156</v>
       </c>
       <c r="E16" s="4">
         <v>0.10043689639314106</v>
@@ -813,36 +814,36 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1.191932059447983</v>
+        <v>1.1894721947077969</v>
       </c>
       <c r="C17" s="3">
-        <v>1.2050975340449024</v>
+        <v>1.2181600638128158</v>
       </c>
       <c r="D17" s="4">
-        <v>0.12514281159497304</v>
+        <v>9.015410522018677E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>0.12177849491282328</v>
+        <v>8.3969636079482032E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>1.189806412583182</v>
+        <v>1.1885458167330678</v>
       </c>
       <c r="C18" s="3">
-        <v>1.2181600638128158</v>
+        <v>1.2050975340449024</v>
       </c>
       <c r="D18" s="4">
-        <v>9.0336507589523593E-2</v>
+        <v>0.12432820665230206</v>
       </c>
       <c r="E18" s="4">
-        <v>8.3969636079482032E-2</v>
+        <v>0.12177849491282328</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -850,13 +851,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1806024774774775</v>
+        <v>1.1783583079167219</v>
       </c>
       <c r="C19" s="3">
         <v>1.1951189749847468</v>
       </c>
       <c r="D19" s="4">
-        <v>8.7643110935649429E-2</v>
+        <v>8.6527980172344546E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.647707486941382E-2</v>
@@ -867,13 +868,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.173496859108585</v>
+        <v>1.1715328467153285</v>
       </c>
       <c r="C20" s="3">
         <v>1.19892610585528</v>
       </c>
       <c r="D20" s="4">
-        <v>8.854456363395577E-2</v>
+        <v>8.7978857411020822E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2772256090329006E-2</v>
@@ -884,13 +885,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2353610612230381</v>
+        <v>1.2347482642497818</v>
       </c>
       <c r="C21" s="7">
         <v>1.2514612346390315</v>
       </c>
       <c r="D21" s="8">
-        <v>0.1100828895559551</v>
+        <v>0.11000947655741183</v>
       </c>
       <c r="E21" s="8">
         <v>0.10421525499788266</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AABEEAD-01A5-4903-8D41-AF9280D48E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C978B2-8D50-4BD6-95DD-E327F965F7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -178,15 +177,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -194,6 +185,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -531,16 +528,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17233115-4901-4354-B5A2-D6FF1650C878}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.90625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -557,341 +555,341 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>1.4036752522970328</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B2" s="5">
+        <v>1.4088096641131411</v>
+      </c>
+      <c r="C2" s="5">
         <v>1.4125986193293885</v>
       </c>
-      <c r="D2" s="4">
-        <v>0.32502692646626846</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="6">
+        <v>0.32140151515151516</v>
+      </c>
+      <c r="E2" s="6">
         <v>0.12716926115787988</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>1.3620370370370372</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="5">
+        <v>1.3645112781954885</v>
+      </c>
+      <c r="C3" s="5">
         <v>1.3683473389355745</v>
       </c>
-      <c r="D3" s="4">
-        <v>0.1735404392072844</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="6">
+        <v>0.17339382561535252</v>
+      </c>
+      <c r="E3" s="6">
         <v>0.16958814308108877</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>1.3247992728374489</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="5">
+        <v>1.3275555555555556</v>
+      </c>
+      <c r="C4" s="5">
         <v>1.3266591991038925</v>
       </c>
-      <c r="D4" s="4">
-        <v>0.21293548387096775</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="6">
+        <v>0.21277266422897489</v>
+      </c>
+      <c r="E4" s="6">
         <v>0.2066550925925926</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>1.2977213298468435</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="5">
+        <v>1.2985618059348263</v>
+      </c>
+      <c r="C5" s="5">
         <v>1.3382928739232578</v>
       </c>
-      <c r="D5" s="4">
-        <v>8.3309992842249395E-2</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="6">
+        <v>8.3253762560814806E-2</v>
+      </c>
+      <c r="E5" s="6">
         <v>9.9015274870124834E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>1.2475679302247569</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="5">
+        <v>1.2472131147540984</v>
+      </c>
+      <c r="C6" s="5">
         <v>1.2541574910775306</v>
       </c>
-      <c r="D6" s="4">
-        <v>0.19940132778140102</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="6">
+        <v>0.20401678957842104</v>
+      </c>
+      <c r="E6" s="6">
         <v>0.13839234107842829</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3">
-        <v>1.2289702461124035</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="5">
+        <v>1.229574773053034</v>
+      </c>
+      <c r="C7" s="5">
         <v>1.2230263890435364</v>
       </c>
-      <c r="D7" s="4">
-        <v>9.7879888301633522E-2</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="6">
+        <v>9.7723823975720783E-2</v>
+      </c>
+      <c r="E7" s="6">
         <v>0.10156515052133988</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>1.2263596276335129</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="5">
+        <v>1.2265051044747637</v>
+      </c>
+      <c r="C8" s="5">
         <v>1.198581560283688</v>
       </c>
-      <c r="D8" s="4">
-        <v>9.9659176359144133E-2</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="6">
+        <v>9.9577217234335658E-2</v>
+      </c>
+      <c r="E8" s="6">
         <v>8.9737470167064445E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3">
-        <v>1.2254604331107064</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="5">
+        <v>1.2236686390532545</v>
+      </c>
+      <c r="C9" s="5">
         <v>1.3143807412100095</v>
       </c>
-      <c r="D9" s="4">
-        <v>6.9682823980707118E-2</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="6">
+        <v>6.9568319657509814E-2</v>
+      </c>
+      <c r="E9" s="6">
         <v>7.4310328594294317E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="3">
-        <v>1.22349251315257</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="5">
+        <v>1.223547973572626</v>
+      </c>
+      <c r="C10" s="5">
         <v>1.2364970197157266</v>
       </c>
-      <c r="D10" s="4">
-        <v>0.11138532968209428</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="6">
+        <v>0.11087422373830141</v>
+      </c>
+      <c r="E10" s="6">
         <v>0.10959138142423572</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>1.2088840736728061</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" s="5">
+        <v>1.2095959595959596</v>
+      </c>
+      <c r="C11" s="5">
         <v>1.2062543921293043</v>
       </c>
-      <c r="D11" s="4">
-        <v>9.3781751676488515E-2</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="6">
+        <v>9.3477063498308283E-2</v>
+      </c>
+      <c r="E11" s="6">
         <v>9.5168032101655239E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>1.2041373926619829</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="5">
+        <v>1.2041587901701323</v>
+      </c>
+      <c r="C12" s="5">
         <v>1.3296387520525452</v>
       </c>
-      <c r="D12" s="4">
-        <v>8.843936621906176E-2</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="6">
+        <v>8.8437876153537515E-2</v>
+      </c>
+      <c r="E12" s="6">
         <v>8.6795410817359087E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1.1981082501313716</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.2106203312763884</v>
+      </c>
+      <c r="D13" s="6">
+        <v>9.8448008277289181E-2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.10424743105754093</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
-        <v>1.1978021978021978</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B14" s="5">
+        <v>1.1970178926441353</v>
+      </c>
+      <c r="C14" s="5">
         <v>1.2132674396502567</v>
       </c>
-      <c r="D13" s="4">
-        <v>8.1564227264428107E-2</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D14" s="6">
+        <v>8.1206309229750889E-2</v>
+      </c>
+      <c r="E14" s="6">
         <v>8.2431098506807896E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3">
-        <v>1.1977289113193945</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1.2106203312763884</v>
-      </c>
-      <c r="D14" s="4">
-        <v>9.8657419756379483E-2</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0.10424743105754093</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
-        <v>1.1961577350859456</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B15" s="5">
+        <v>1.1951700344997536</v>
+      </c>
+      <c r="C15" s="5">
         <v>1.2410423452768728</v>
       </c>
-      <c r="D15" s="4">
-        <v>8.4998495982123667E-2</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="D15" s="6">
+        <v>8.4753550543024234E-2</v>
+      </c>
+      <c r="E15" s="6">
         <v>8.3184950065804758E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="3">
-        <v>1.1922305307313517</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B16" s="5">
+        <v>1.1903404027802531</v>
+      </c>
+      <c r="C16" s="5">
         <v>1.1877350776778415</v>
       </c>
-      <c r="D16" s="4">
-        <v>0.11219791687982156</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="6">
+        <v>0.11197589255423178</v>
+      </c>
+      <c r="E16" s="6">
         <v>0.10043689639314106</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
-        <v>1.1894721947077969</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="5">
+        <v>1.1891259463179626</v>
+      </c>
+      <c r="C17" s="5">
         <v>1.2181600638128158</v>
       </c>
-      <c r="D17" s="4">
-        <v>9.015410522018677E-2</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17" s="6">
+        <v>9.080909465895029E-2</v>
+      </c>
+      <c r="E17" s="6">
         <v>8.3969636079482032E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="3">
-        <v>1.1885458167330678</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B18" s="5">
+        <v>1.1887908465044119</v>
+      </c>
+      <c r="C18" s="5">
         <v>1.2050975340449024</v>
       </c>
-      <c r="D18" s="4">
-        <v>0.12432820665230206</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="6">
+        <v>0.12401842298303209</v>
+      </c>
+      <c r="E18" s="6">
         <v>0.12177849491282328</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
-        <v>1.1783583079167219</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19" s="5">
+        <v>1.1787377133988619</v>
+      </c>
+      <c r="C19" s="5">
         <v>1.1951189749847468</v>
       </c>
-      <c r="D19" s="4">
-        <v>8.6527980172344546E-2</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="6">
+        <v>8.594548930683385E-2</v>
+      </c>
+      <c r="E19" s="6">
         <v>8.647707486941382E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
-        <v>1.1715328467153285</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="5">
+        <v>1.1720930232558142</v>
+      </c>
+      <c r="C20" s="5">
         <v>1.19892610585528</v>
       </c>
-      <c r="D20" s="4">
-        <v>8.7978857411020822E-2</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="6">
+        <v>8.7626765121910283E-2</v>
+      </c>
+      <c r="E20" s="6">
         <v>9.2772256090329006E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2347482642497818</v>
+        <v>1.2351229318828481</v>
       </c>
       <c r="C21" s="7">
         <v>1.2514612346390315</v>
       </c>
       <c r="D21" s="8">
-        <v>0.11000947655741183</v>
+        <v>0.10988630209224104</v>
       </c>
       <c r="E21" s="8">
         <v>0.10421525499788266</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C978B2-8D50-4BD6-95DD-E327F965F7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D5255D-EA6E-4E77-9C4F-8869452BA54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\ %;\-0.00\ %;0.00\ %"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -132,6 +132,11 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -178,19 +183,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -530,7 +538,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" style="3" bestFit="1" customWidth="1"/>
@@ -555,343 +563,343 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4088096641131411</v>
+        <v>1.4091708174626429</v>
       </c>
       <c r="C2" s="5">
         <v>1.4125986193293885</v>
       </c>
       <c r="D2" s="6">
-        <v>0.32140151515151516</v>
+        <v>0.32072546163604754</v>
       </c>
       <c r="E2" s="6">
         <v>0.12716926115787988</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3645112781954885</v>
+        <v>1.3630382775119618</v>
       </c>
       <c r="C3" s="5">
         <v>1.3683473389355745</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17339382561535252</v>
+        <v>0.17336305666442015</v>
       </c>
       <c r="E3" s="6">
         <v>0.16958814308108877</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3275555555555556</v>
+        <v>1.3280789628756631</v>
       </c>
       <c r="C4" s="5">
         <v>1.3266591991038925</v>
       </c>
       <c r="D4" s="6">
-        <v>0.21277266422897489</v>
+        <v>0.21265664160401002</v>
       </c>
       <c r="E4" s="6">
         <v>0.2066550925925926</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.2985618059348263</v>
+        <v>1.299765385309511</v>
       </c>
       <c r="C5" s="5">
         <v>1.3382928739232578</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3253762560814806E-2</v>
+        <v>8.3337093353787847E-2</v>
       </c>
       <c r="E5" s="6">
         <v>9.9015274870124834E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2472131147540984</v>
+        <v>1.2475376475376476</v>
       </c>
       <c r="C6" s="5">
         <v>1.2541574910775306</v>
       </c>
       <c r="D6" s="6">
-        <v>0.20401678957842104</v>
+        <v>0.20543821803040185</v>
       </c>
       <c r="E6" s="6">
         <v>0.13839234107842829</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.229574773053034</v>
+        <v>1.2303770452928624</v>
       </c>
       <c r="C7" s="5">
         <v>1.2230263890435364</v>
       </c>
       <c r="D7" s="6">
-        <v>9.7723823975720783E-2</v>
+        <v>9.7532206212271891E-2</v>
       </c>
       <c r="E7" s="6">
         <v>0.10156515052133988</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="5">
-        <v>1.2265051044747637</v>
+        <v>1.2263936291240045</v>
       </c>
       <c r="C8" s="5">
         <v>1.198581560283688</v>
       </c>
       <c r="D8" s="6">
-        <v>9.9577217234335658E-2</v>
+        <v>9.9452202034678153E-2</v>
       </c>
       <c r="E8" s="6">
         <v>8.9737470167064445E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.2249216300940438</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1.2364970197157266</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.11065462705011328</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.10959138142423572</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5">
-        <v>1.2236686390532545</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B10" s="5">
+        <v>1.2238951896754009</v>
+      </c>
+      <c r="C10" s="5">
         <v>1.3143807412100095</v>
       </c>
-      <c r="D9" s="6">
-        <v>6.9568319657509814E-2</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D10" s="6">
+        <v>6.9430867817964592E-2</v>
+      </c>
+      <c r="E10" s="6">
         <v>7.4310328594294317E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>1.223547973572626</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1.2364970197157266</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.11087422373830141</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.10959138142423572</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2095959595959596</v>
+        <v>1.2091080008355963</v>
       </c>
       <c r="C11" s="5">
         <v>1.2062543921293043</v>
       </c>
       <c r="D11" s="6">
-        <v>9.3477063498308283E-2</v>
+        <v>9.3293835629786992E-2</v>
       </c>
       <c r="E11" s="6">
         <v>9.5168032101655239E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.2041587901701323</v>
+        <v>1.2045795795795797</v>
       </c>
       <c r="C12" s="5">
         <v>1.3296387520525452</v>
       </c>
       <c r="D12" s="6">
-        <v>8.8437876153537515E-2</v>
+        <v>8.842566468616192E-2</v>
       </c>
       <c r="E12" s="6">
         <v>8.6795410817359087E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>1.1981082501313716</v>
+        <v>1.1974233983286908</v>
       </c>
       <c r="C13" s="5">
         <v>1.2106203312763884</v>
       </c>
       <c r="D13" s="6">
-        <v>9.8448008277289181E-2</v>
+        <v>9.8398286937901494E-2</v>
       </c>
       <c r="E13" s="6">
         <v>0.10424743105754093</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>1.1970178926441353</v>
+        <v>1.1963686599565817</v>
       </c>
       <c r="C14" s="5">
         <v>1.2132674396502567</v>
       </c>
       <c r="D14" s="6">
-        <v>8.1206309229750889E-2</v>
+        <v>8.1201923076923074E-2</v>
       </c>
       <c r="E14" s="6">
         <v>8.2431098506807896E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <v>1.1951700344997536</v>
+        <v>1.1945259042033234</v>
       </c>
       <c r="C15" s="5">
         <v>1.2410423452768728</v>
       </c>
       <c r="D15" s="6">
-        <v>8.4753550543024234E-2</v>
+        <v>8.4839940288605073E-2</v>
       </c>
       <c r="E15" s="6">
         <v>8.3184950065804758E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1903404027802531</v>
+        <v>1.1898443029016277</v>
       </c>
       <c r="C16" s="5">
         <v>1.1877350776778415</v>
       </c>
       <c r="D16" s="6">
-        <v>0.11197589255423178</v>
+        <v>0.11199619545832838</v>
       </c>
       <c r="E16" s="6">
         <v>0.10043689639314106</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="5">
-        <v>1.1891259463179626</v>
+        <v>1.1896811276857806</v>
       </c>
       <c r="C17" s="5">
         <v>1.2181600638128158</v>
       </c>
       <c r="D17" s="6">
-        <v>9.080909465895029E-2</v>
+        <v>9.0566552224191563E-2</v>
       </c>
       <c r="E17" s="6">
         <v>8.3969636079482032E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1887908465044119</v>
+        <v>1.1884504331087584</v>
       </c>
       <c r="C18" s="5">
         <v>1.2050975340449024</v>
       </c>
       <c r="D18" s="6">
-        <v>0.12401842298303209</v>
+        <v>0.12396644911887178</v>
       </c>
       <c r="E18" s="6">
         <v>0.12177849491282328</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="5">
-        <v>1.1787377133988619</v>
+        <v>1.1789338471419397</v>
       </c>
       <c r="C19" s="5">
         <v>1.1951189749847468</v>
       </c>
       <c r="D19" s="6">
-        <v>8.594548930683385E-2</v>
+        <v>8.5936637597968865E-2</v>
       </c>
       <c r="E19" s="6">
         <v>8.647707486941382E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="5">
-        <v>1.1720930232558142</v>
+        <v>1.1720108695652174</v>
       </c>
       <c r="C20" s="5">
         <v>1.19892610585528</v>
       </c>
       <c r="D20" s="6">
-        <v>8.7626765121910283E-2</v>
+        <v>8.7435848697966168E-2</v>
       </c>
       <c r="E20" s="6">
         <v>9.2772256090329006E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
-        <v>1.2351229318828481</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="B21" s="8">
+        <v>1.2352789630464536</v>
+      </c>
+      <c r="C21" s="8">
         <v>1.2514612346390315</v>
       </c>
-      <c r="D21" s="8">
-        <v>0.10988630209224104</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="D21" s="9">
+        <v>0.10980481599449783</v>
+      </c>
+      <c r="E21" s="9">
         <v>0.10421525499788266</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D5255D-EA6E-4E77-9C4F-8869452BA54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68966F04-99AF-47C8-A5BF-71582965238C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,6 +137,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -568,16 +569,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4091708174626429</v>
+        <v>1.4018804974218986</v>
       </c>
       <c r="C2" s="5">
-        <v>1.4125986193293885</v>
+        <v>1.4160264900662252</v>
       </c>
       <c r="D2" s="6">
-        <v>0.32072546163604754</v>
+        <v>0.32363190184049079</v>
       </c>
       <c r="E2" s="6">
-        <v>0.12716926115787988</v>
+        <v>0.12812897751378871</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -585,16 +586,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3630382775119618</v>
+        <v>1.3564571074636109</v>
       </c>
       <c r="C3" s="5">
-        <v>1.3683473389355745</v>
+        <v>1.3636638452237</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17336305666442015</v>
+        <v>0.17492821929681998</v>
       </c>
       <c r="E3" s="6">
-        <v>0.16958814308108877</v>
+        <v>0.17008586559720293</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -602,16 +603,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3280789628756631</v>
+        <v>1.3259609517998778</v>
       </c>
       <c r="C4" s="5">
-        <v>1.3266591991038925</v>
+        <v>1.3182769967095422</v>
       </c>
       <c r="D4" s="6">
-        <v>0.21265664160401002</v>
+        <v>0.2140944419045131</v>
       </c>
       <c r="E4" s="6">
-        <v>0.2066550925925926</v>
+        <v>0.20760751436112404</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -619,16 +620,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.299765385309511</v>
+        <v>1.3009380863039399</v>
       </c>
       <c r="C5" s="5">
-        <v>1.3382928739232578</v>
+        <v>1.3363945578231291</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3337093353787847E-2</v>
+        <v>8.3322911455727858E-2</v>
       </c>
       <c r="E5" s="6">
-        <v>9.9015274870124834E-2</v>
+        <v>9.8396867365038984E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -636,16 +637,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2475376475376476</v>
+        <v>1.2469031053792636</v>
       </c>
       <c r="C6" s="5">
-        <v>1.2541574910775306</v>
+        <v>1.2506318793314311</v>
       </c>
       <c r="D6" s="6">
-        <v>0.20543821803040185</v>
+        <v>0.19709359688289102</v>
       </c>
       <c r="E6" s="6">
-        <v>0.13839234107842829</v>
+        <v>0.13894395794863662</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -653,67 +654,67 @@
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.2303770452928624</v>
+        <v>1.2305043050430504</v>
       </c>
       <c r="C7" s="5">
-        <v>1.2230263890435364</v>
+        <v>1.2233021358291336</v>
       </c>
       <c r="D7" s="6">
-        <v>9.7532206212271891E-2</v>
+        <v>9.7513583534237697E-2</v>
       </c>
       <c r="E7" s="6">
-        <v>0.10156515052133988</v>
+        <v>0.10215864376861693</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5">
-        <v>1.2263936291240045</v>
+        <v>1.225799877725698</v>
       </c>
       <c r="C8" s="5">
-        <v>1.198581560283688</v>
+        <v>1.2797202797202798</v>
       </c>
       <c r="D8" s="6">
-        <v>9.9452202034678153E-2</v>
+        <v>6.9518034737766701E-2</v>
       </c>
       <c r="E8" s="6">
-        <v>8.9737470167064445E-2</v>
+        <v>7.4333747496006283E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>1.2249216300940438</v>
+        <v>1.2256632804024064</v>
       </c>
       <c r="C9" s="5">
-        <v>1.2364970197157266</v>
+        <v>1.2005768537435404</v>
       </c>
       <c r="D9" s="6">
-        <v>0.11065462705011328</v>
+        <v>9.9615841856535103E-2</v>
       </c>
       <c r="E9" s="6">
-        <v>0.10959138142423572</v>
+        <v>8.9587752069852825E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>1.2238951896754009</v>
+        <v>1.2236493374108053</v>
       </c>
       <c r="C10" s="5">
-        <v>1.3143807412100095</v>
+        <v>1.2377594597278776</v>
       </c>
       <c r="D10" s="6">
-        <v>6.9430867817964592E-2</v>
+        <v>0.11099921927154641</v>
       </c>
       <c r="E10" s="6">
-        <v>7.4310328594294317E-2</v>
+        <v>0.10995238927229842</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -721,16 +722,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2091080008355963</v>
+        <v>1.2070021881838076</v>
       </c>
       <c r="C11" s="5">
-        <v>1.2062543921293043</v>
+        <v>1.2108353854896761</v>
       </c>
       <c r="D11" s="6">
-        <v>9.3293835629786992E-2</v>
+        <v>9.3362479315205624E-2</v>
       </c>
       <c r="E11" s="6">
-        <v>9.5168032101655239E-2</v>
+        <v>9.5838931048255332E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -738,33 +739,33 @@
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.2045795795795797</v>
+        <v>1.2062992125984253</v>
       </c>
       <c r="C12" s="5">
-        <v>1.3296387520525452</v>
+        <v>1.3439293598233997</v>
       </c>
       <c r="D12" s="6">
-        <v>8.842566468616192E-2</v>
+        <v>8.8560370977302044E-2</v>
       </c>
       <c r="E12" s="6">
-        <v>8.6795410817359087E-2</v>
+        <v>8.7098634877908088E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="5">
-        <v>1.1974233983286908</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="C13" s="5">
-        <v>1.2106203312763884</v>
+        <v>1.2337531486146094</v>
       </c>
       <c r="D13" s="6">
-        <v>9.8398286937901494E-2</v>
+        <v>8.4775011864187413E-2</v>
       </c>
       <c r="E13" s="6">
-        <v>0.10424743105754093</v>
+        <v>8.3480528219362429E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -772,33 +773,33 @@
         <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>1.1963686599565817</v>
+        <v>1.1996314496314495</v>
       </c>
       <c r="C14" s="5">
-        <v>1.2132674396502567</v>
+        <v>1.2143004753048152</v>
       </c>
       <c r="D14" s="6">
-        <v>8.1201923076923074E-2</v>
+        <v>8.1583563016787777E-2</v>
       </c>
       <c r="E14" s="6">
-        <v>8.2431098506807896E-2</v>
+        <v>8.3268803882091791E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="5">
-        <v>1.1945259042033234</v>
+        <v>1.1974256707759245</v>
       </c>
       <c r="C15" s="5">
-        <v>1.2410423452768728</v>
+        <v>1.2123443801507978</v>
       </c>
       <c r="D15" s="6">
-        <v>8.4839940288605073E-2</v>
+        <v>9.8923959827833571E-2</v>
       </c>
       <c r="E15" s="6">
-        <v>8.3184950065804758E-2</v>
+        <v>0.10461340915344401</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -806,50 +807,50 @@
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1898443029016277</v>
+        <v>1.1923851363719569</v>
       </c>
       <c r="C16" s="5">
-        <v>1.1877350776778415</v>
+        <v>1.1878154917319408</v>
       </c>
       <c r="D16" s="6">
-        <v>0.11199619545832838</v>
+        <v>0.1124236001070113</v>
       </c>
       <c r="E16" s="6">
-        <v>0.10043689639314106</v>
+        <v>0.10094354541141742</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>1.1896811276857806</v>
+        <v>1.1901330931652156</v>
       </c>
       <c r="C17" s="5">
-        <v>1.2181600638128158</v>
+        <v>1.2014754261788456</v>
       </c>
       <c r="D17" s="6">
-        <v>9.0566552224191563E-2</v>
+        <v>0.12442878310567668</v>
       </c>
       <c r="E17" s="6">
-        <v>8.3969636079482032E-2</v>
+        <v>0.12181230873852431</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1884504331087584</v>
+        <v>1.1898049266695143</v>
       </c>
       <c r="C18" s="5">
-        <v>1.2050975340449024</v>
+        <v>1.222510448191382</v>
       </c>
       <c r="D18" s="6">
-        <v>0.12396644911887178</v>
+        <v>8.9184349879995434E-2</v>
       </c>
       <c r="E18" s="6">
-        <v>0.12177849491282328</v>
+        <v>8.3909741704556451E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -857,16 +858,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="5">
-        <v>1.1789338471419397</v>
+        <v>1.1800346990524488</v>
       </c>
       <c r="C19" s="5">
-        <v>1.1951189749847468</v>
+        <v>1.1985787603632057</v>
       </c>
       <c r="D19" s="6">
-        <v>8.5936637597968865E-2</v>
+        <v>8.6881406242753118E-2</v>
       </c>
       <c r="E19" s="6">
-        <v>8.647707486941382E-2</v>
+        <v>8.7010786177204757E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -874,16 +875,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="5">
-        <v>1.1720108695652174</v>
+        <v>1.1748370643241712</v>
       </c>
       <c r="C20" s="5">
-        <v>1.19892610585528</v>
+        <v>1.2005502063273727</v>
       </c>
       <c r="D20" s="6">
-        <v>8.7435848697966168E-2</v>
+        <v>8.7529143310680096E-2</v>
       </c>
       <c r="E20" s="6">
-        <v>9.2772256090329006E-2</v>
+        <v>9.3308006263315965E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
@@ -891,16 +892,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="8">
-        <v>1.2352789630464536</v>
+        <v>1.2351724888453586</v>
       </c>
       <c r="C21" s="8">
-        <v>1.2514612346390315</v>
+        <v>1.25</v>
       </c>
       <c r="D21" s="9">
-        <v>0.10980481599449783</v>
+        <v>0.10979614683604338</v>
       </c>
       <c r="E21" s="9">
-        <v>0.10421525499788266</v>
+        <v>0.10459255888976028</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68966F04-99AF-47C8-A5BF-71582965238C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF78C6C-FC83-4C48-AB64-36EAB6D723FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\ %;\-0.00\ %;0.00\ %"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -131,12 +131,6 @@
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -184,22 +178,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -539,7 +529,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" style="3" bestFit="1" customWidth="1"/>
@@ -564,344 +554,344 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4018804974218986</v>
+        <v>1.4101415775787345</v>
       </c>
       <c r="C2" s="5">
-        <v>1.4160264900662252</v>
+        <v>1.4125986193293885</v>
       </c>
       <c r="D2" s="6">
-        <v>0.32363190184049079</v>
+        <v>0.31939830195644148</v>
       </c>
       <c r="E2" s="6">
-        <v>0.12812897751378871</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.12716926115787988</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3564571074636109</v>
+        <v>1.3625368731563421</v>
       </c>
       <c r="C3" s="5">
-        <v>1.3636638452237</v>
+        <v>1.3683473389355745</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17492821929681998</v>
+        <v>0.17345476872697502</v>
       </c>
       <c r="E3" s="6">
-        <v>0.17008586559720293</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.16958814308108877</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3259609517998778</v>
+        <v>1.3292896813797135</v>
       </c>
       <c r="C4" s="5">
-        <v>1.3182769967095422</v>
+        <v>1.3266591991038925</v>
       </c>
       <c r="D4" s="6">
-        <v>0.2140944419045131</v>
+        <v>0.21195786864931845</v>
       </c>
       <c r="E4" s="6">
-        <v>0.20760751436112404</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.2066550925925926</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.3009380863039399</v>
+        <v>1.2997862486640543</v>
       </c>
       <c r="C5" s="5">
-        <v>1.3363945578231291</v>
+        <v>1.3382928739232578</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3322911455727858E-2</v>
+        <v>8.3424971022676611E-2</v>
       </c>
       <c r="E5" s="6">
-        <v>9.8396867365038984E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>9.9015274870124834E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2469031053792636</v>
+        <v>1.2474226804123711</v>
       </c>
       <c r="C6" s="5">
-        <v>1.2506318793314311</v>
+        <v>1.2541574910775306</v>
       </c>
       <c r="D6" s="6">
-        <v>0.19709359688289102</v>
+        <v>0.20762889011521932</v>
       </c>
       <c r="E6" s="6">
-        <v>0.13894395794863662</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.13839234107842829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.2305043050430504</v>
+        <v>1.2323102155576382</v>
       </c>
       <c r="C7" s="5">
-        <v>1.2233021358291336</v>
+        <v>1.2230263890435364</v>
       </c>
       <c r="D7" s="6">
-        <v>9.7513583534237697E-2</v>
+        <v>9.7215420534138147E-2</v>
       </c>
       <c r="E7" s="6">
-        <v>0.10215864376861693</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.10156515052133988</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1.2264469001685707</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.198581560283688</v>
+      </c>
+      <c r="D8" s="6">
+        <v>9.9318221982457933E-2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>8.9737470167064445E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.2259094427244581</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1.2364970197157266</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.11040493916833122</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.10959138142423572</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5">
-        <v>1.225799877725698</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.2797202797202798</v>
-      </c>
-      <c r="D8" s="6">
-        <v>6.9518034737766701E-2</v>
-      </c>
-      <c r="E8" s="6">
-        <v>7.4333747496006283E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5">
-        <v>1.2256632804024064</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.2005768537435404</v>
-      </c>
-      <c r="D9" s="6">
-        <v>9.9615841856535103E-2</v>
-      </c>
-      <c r="E9" s="6">
-        <v>8.9587752069852825E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="B10" s="5">
-        <v>1.2236493374108053</v>
+        <v>1.2245451025938832</v>
       </c>
       <c r="C10" s="5">
-        <v>1.2377594597278776</v>
+        <v>1.3143807412100095</v>
       </c>
       <c r="D10" s="6">
-        <v>0.11099921927154641</v>
+        <v>6.9223347805113356E-2</v>
       </c>
       <c r="E10" s="6">
-        <v>0.10995238927229842</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>7.4310328594294317E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2070021881838076</v>
+        <v>1.2100475501343808</v>
       </c>
       <c r="C11" s="5">
-        <v>1.2108353854896761</v>
+        <v>1.2062543921293043</v>
       </c>
       <c r="D11" s="6">
-        <v>9.3362479315205624E-2</v>
+        <v>9.3033543622095705E-2</v>
       </c>
       <c r="E11" s="6">
-        <v>9.5838931048255332E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>9.5168032101655239E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.2062992125984253</v>
+        <v>1.2045118343195267</v>
       </c>
       <c r="C12" s="5">
-        <v>1.3439293598233997</v>
+        <v>1.3296387520525452</v>
       </c>
       <c r="D12" s="6">
-        <v>8.8560370977302044E-2</v>
+        <v>8.816720466920995E-2</v>
       </c>
       <c r="E12" s="6">
-        <v>8.7098634877908088E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>8.6795410817359087E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1.1978664831383345</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.2106203312763884</v>
+      </c>
+      <c r="D13" s="6">
+        <v>9.8238734322707147E-2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.10424743105754093</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="5">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1.2337531486146094</v>
-      </c>
-      <c r="D13" s="6">
-        <v>8.4775011864187413E-2</v>
-      </c>
-      <c r="E13" s="6">
-        <v>8.3480528219362429E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="5">
+        <v>1.1969990319457888</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.2410423452768728</v>
+      </c>
+      <c r="D14" s="6">
+        <v>8.4398872502961728E-2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>8.3184950065804758E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5">
-        <v>1.1996314496314495</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.2143004753048152</v>
-      </c>
-      <c r="D14" s="6">
-        <v>8.1583563016787777E-2</v>
-      </c>
-      <c r="E14" s="6">
-        <v>8.3268803882091791E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="B15" s="5">
-        <v>1.1974256707759245</v>
+        <v>1.1967308814944542</v>
       </c>
       <c r="C15" s="5">
-        <v>1.2123443801507978</v>
+        <v>1.2132674396502567</v>
       </c>
       <c r="D15" s="6">
-        <v>9.8923959827833571E-2</v>
+        <v>8.1258004838480141E-2</v>
       </c>
       <c r="E15" s="6">
-        <v>0.10461340915344401</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>8.2431098506807896E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1923851363719569</v>
+        <v>1.1899930020993703</v>
       </c>
       <c r="C16" s="5">
-        <v>1.1878154917319408</v>
+        <v>1.1877350776778415</v>
       </c>
       <c r="D16" s="6">
-        <v>0.1124236001070113</v>
+        <v>0.11180002738279188</v>
       </c>
       <c r="E16" s="6">
-        <v>0.10094354541141742</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.10043689639314106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>1.1901330931652156</v>
+        <v>1.1896928781972047</v>
       </c>
       <c r="C17" s="5">
-        <v>1.2014754261788456</v>
+        <v>1.2050975340449024</v>
       </c>
       <c r="D17" s="6">
-        <v>0.12442878310567668</v>
+        <v>0.12385326502973562</v>
       </c>
       <c r="E17" s="6">
-        <v>0.12181230873852431</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>0.12177849491282328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1898049266695143</v>
+        <v>1.1895945945945947</v>
       </c>
       <c r="C18" s="5">
-        <v>1.222510448191382</v>
+        <v>1.2181600638128158</v>
       </c>
       <c r="D18" s="6">
-        <v>8.9184349879995434E-2</v>
+        <v>9.0535382206127044E-2</v>
       </c>
       <c r="E18" s="6">
-        <v>8.3909741704556451E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>8.3969636079482032E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="5">
-        <v>1.1800346990524488</v>
+        <v>1.1786666666666665</v>
       </c>
       <c r="C19" s="5">
-        <v>1.1985787603632057</v>
+        <v>1.1951189749847468</v>
       </c>
       <c r="D19" s="6">
-        <v>8.6881406242753118E-2</v>
+        <v>8.5910652920962199E-2</v>
       </c>
       <c r="E19" s="6">
-        <v>8.7010786177204757E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>8.647707486941382E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="5">
-        <v>1.1748370643241712</v>
+        <v>1.1735159817351599</v>
       </c>
       <c r="C20" s="5">
-        <v>1.2005502063273727</v>
+        <v>1.19892610585528</v>
       </c>
       <c r="D20" s="6">
-        <v>8.7529143310680096E-2</v>
+        <v>8.7210119465917071E-2</v>
       </c>
       <c r="E20" s="6">
-        <v>9.3308006263315965E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+        <v>9.2772256090329006E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="8">
-        <v>1.2351724888453586</v>
+        <v>1.235867896156386</v>
       </c>
       <c r="C21" s="8">
-        <v>1.25</v>
+        <v>1.2514612346390315</v>
       </c>
       <c r="D21" s="9">
-        <v>0.10979614683604338</v>
+        <v>0.10969234582382059</v>
       </c>
       <c r="E21" s="9">
-        <v>0.10459255888976028</v>
+        <v>0.10421525499788266</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF78C6C-FC83-4C48-AB64-36EAB6D723FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF2D57-CBE0-4D99-8004-CB14A9CA9A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -559,16 +559,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4101415775787345</v>
+        <v>1.4050749408361822</v>
       </c>
       <c r="C2" s="5">
-        <v>1.4125986193293885</v>
+        <v>1.4093913836334626</v>
       </c>
       <c r="D2" s="6">
-        <v>0.31939830195644148</v>
+        <v>0.31590314407941189</v>
       </c>
       <c r="E2" s="6">
-        <v>0.12716926115787988</v>
+        <v>0.12703422713847223</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -576,16 +576,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3625368731563421</v>
+        <v>1.3655737704918034</v>
       </c>
       <c r="C3" s="5">
-        <v>1.3683473389355745</v>
+        <v>1.3814776808619806</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17345476872697502</v>
+        <v>0.17232449738688263</v>
       </c>
       <c r="E3" s="6">
-        <v>0.16958814308108877</v>
+        <v>0.17001046755059315</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -593,16 +593,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3292896813797135</v>
+        <v>1.3296762833536502</v>
       </c>
       <c r="C4" s="5">
-        <v>1.3266591991038925</v>
+        <v>1.3202993934701253</v>
       </c>
       <c r="D4" s="6">
-        <v>0.21195786864931845</v>
+        <v>0.21097902497571011</v>
       </c>
       <c r="E4" s="6">
-        <v>0.2066550925925926</v>
+        <v>0.20542933644389066</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -610,16 +610,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.2997862486640543</v>
+        <v>1.300588427590716</v>
       </c>
       <c r="C5" s="5">
-        <v>1.3382928739232578</v>
+        <v>1.3376422649992976</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3424971022676611E-2</v>
+        <v>8.3478877851762903E-2</v>
       </c>
       <c r="E5" s="6">
-        <v>9.9015274870124834E-2</v>
+        <v>9.9617877188807866E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -627,16 +627,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2474226804123711</v>
+        <v>1.2459742945782242</v>
       </c>
       <c r="C6" s="5">
-        <v>1.2541574910775306</v>
+        <v>1.2508368200836821</v>
       </c>
       <c r="D6" s="6">
-        <v>0.20762889011521932</v>
+        <v>0.22639174568136591</v>
       </c>
       <c r="E6" s="6">
-        <v>0.13839234107842829</v>
+        <v>0.13768735177486102</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -644,50 +644,50 @@
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.2323102155576382</v>
+        <v>1.2342102460325912</v>
       </c>
       <c r="C7" s="5">
-        <v>1.2230263890435364</v>
+        <v>1.225040749796251</v>
       </c>
       <c r="D7" s="6">
-        <v>9.7215420534138147E-2</v>
+        <v>9.7698278911989345E-2</v>
       </c>
       <c r="E7" s="6">
-        <v>0.10156515052133988</v>
+        <v>0.10101779337456648</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5">
-        <v>1.2264469001685707</v>
+        <v>1.2280732652342374</v>
       </c>
       <c r="C8" s="5">
-        <v>1.198581560283688</v>
+        <v>1.2349717561757021</v>
       </c>
       <c r="D8" s="6">
-        <v>9.9318221982457933E-2</v>
+        <v>0.11028669101079948</v>
       </c>
       <c r="E8" s="6">
-        <v>8.9737470167064445E-2</v>
+        <v>0.10856154353079008</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>1.2259094427244581</v>
+        <v>1.2280701754385965</v>
       </c>
       <c r="C9" s="5">
-        <v>1.2364970197157266</v>
+        <v>1.1993172005221406</v>
       </c>
       <c r="D9" s="6">
-        <v>0.11040493916833122</v>
+        <v>9.9462891871877152E-2</v>
       </c>
       <c r="E9" s="6">
-        <v>0.10959138142423572</v>
+        <v>8.9892407119904677E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -695,16 +695,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>1.2245451025938832</v>
+        <v>1.2245256500351371</v>
       </c>
       <c r="C10" s="5">
-        <v>1.3143807412100095</v>
+        <v>1.3068905616676318</v>
       </c>
       <c r="D10" s="6">
-        <v>6.9223347805113356E-2</v>
+        <v>6.9782267555904276E-2</v>
       </c>
       <c r="E10" s="6">
-        <v>7.4310328594294317E-2</v>
+        <v>7.4165530420965617E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -712,16 +712,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2100475501343808</v>
+        <v>1.2122936824132045</v>
       </c>
       <c r="C11" s="5">
-        <v>1.2062543921293043</v>
+        <v>1.2055681450307543</v>
       </c>
       <c r="D11" s="6">
-        <v>9.3033543622095705E-2</v>
+        <v>9.2140684543579349E-2</v>
       </c>
       <c r="E11" s="6">
-        <v>9.5168032101655239E-2</v>
+        <v>9.4505292785902223E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -729,16 +729,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.2045118343195267</v>
+        <v>1.206989247311828</v>
       </c>
       <c r="C12" s="5">
-        <v>1.3296387520525452</v>
+        <v>1.3231753197893152</v>
       </c>
       <c r="D12" s="6">
-        <v>8.816720466920995E-2</v>
+        <v>8.8047337278106513E-2</v>
       </c>
       <c r="E12" s="6">
-        <v>8.6795410817359087E-2</v>
+        <v>8.7064758098856831E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -746,67 +746,67 @@
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>1.1978664831383345</v>
+        <v>1.2012628255722178</v>
       </c>
       <c r="C13" s="5">
-        <v>1.2106203312763884</v>
+        <v>1.2062227566511348</v>
       </c>
       <c r="D13" s="6">
-        <v>9.8238734322707147E-2</v>
+        <v>9.8171393150472644E-2</v>
       </c>
       <c r="E13" s="6">
-        <v>0.10424743105754093</v>
+        <v>0.10362605526307592</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>1.1969990319457888</v>
+        <v>1.2005710206995002</v>
       </c>
       <c r="C14" s="5">
-        <v>1.2410423452768728</v>
+        <v>1.2073467966573816</v>
       </c>
       <c r="D14" s="6">
-        <v>8.4398872502961728E-2</v>
+        <v>8.0651660814000339E-2</v>
       </c>
       <c r="E14" s="6">
-        <v>8.3184950065804758E-2</v>
+        <v>8.1383981070856773E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B15" s="5">
-        <v>1.1967308814944542</v>
+        <v>1.1977827050997782</v>
       </c>
       <c r="C15" s="5">
-        <v>1.2132674396502567</v>
+        <v>1.2418664383561644</v>
       </c>
       <c r="D15" s="6">
-        <v>8.1258004838480141E-2</v>
+        <v>8.4182625900623434E-2</v>
       </c>
       <c r="E15" s="6">
-        <v>8.2431098506807896E-2</v>
+        <v>8.2576266393297751E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1899930020993703</v>
+        <v>1.1932499999999999</v>
       </c>
       <c r="C16" s="5">
-        <v>1.1877350776778415</v>
+        <v>1.2172688303735455</v>
       </c>
       <c r="D16" s="6">
-        <v>0.11180002738279188</v>
+        <v>9.2453484340691089E-2</v>
       </c>
       <c r="E16" s="6">
-        <v>0.10043689639314106</v>
+        <v>8.3293378354943021E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -814,67 +814,67 @@
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>1.1896928781972047</v>
+        <v>1.1905177682703223</v>
       </c>
       <c r="C17" s="5">
-        <v>1.2050975340449024</v>
+        <v>1.2026913372582002</v>
       </c>
       <c r="D17" s="6">
-        <v>0.12385326502973562</v>
+        <v>0.12309230041700701</v>
       </c>
       <c r="E17" s="6">
-        <v>0.12177849491282328</v>
+        <v>0.12134758070277497</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1895945945945947</v>
+        <v>1.1877828054298643</v>
       </c>
       <c r="C18" s="5">
-        <v>1.2181600638128158</v>
+        <v>1.1921855146124523</v>
       </c>
       <c r="D18" s="6">
-        <v>9.0535382206127044E-2</v>
+        <v>0.11060665641868946</v>
       </c>
       <c r="E18" s="6">
-        <v>8.3969636079482032E-2</v>
+        <v>9.9966656610723875E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="5">
-        <v>1.1786666666666665</v>
+        <v>1.18021978021978</v>
       </c>
       <c r="C19" s="5">
-        <v>1.1951189749847468</v>
+        <v>1.1960830580462483</v>
       </c>
       <c r="D19" s="6">
-        <v>8.5910652920962199E-2</v>
+        <v>8.720187393526406E-2</v>
       </c>
       <c r="E19" s="6">
-        <v>8.647707486941382E-2</v>
+        <v>9.2038396386222479E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="5">
-        <v>1.1735159817351599</v>
+        <v>1.1781814001609381</v>
       </c>
       <c r="C20" s="5">
-        <v>1.19892610585528</v>
+        <v>1.1936572199730096</v>
       </c>
       <c r="D20" s="6">
-        <v>8.7210119465917071E-2</v>
+        <v>8.6279060541140998E-2</v>
       </c>
       <c r="E20" s="6">
-        <v>9.2772256090329006E-2</v>
+        <v>8.5774643811434695E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -882,16 +882,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="8">
-        <v>1.235867896156386</v>
+        <v>1.2367901648179573</v>
       </c>
       <c r="C21" s="8">
-        <v>1.2514612346390315</v>
+        <v>1.2499860599977697</v>
       </c>
       <c r="D21" s="9">
-        <v>0.10969234582382059</v>
+        <v>0.11013960069852489</v>
       </c>
       <c r="E21" s="9">
-        <v>0.10421525499788266</v>
+        <v>0.10371404902041577</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF2D57-CBE0-4D99-8004-CB14A9CA9A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CDF003-4C17-4137-B69B-63FDEDCCC08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\ %;\-0.00\ %;0.00\ %"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -131,6 +131,12 @@
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -178,18 +184,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -554,341 +564,341 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4050749408361822</v>
+        <v>1.4051471525035035</v>
       </c>
       <c r="C2" s="5">
         <v>1.4093913836334626</v>
       </c>
       <c r="D2" s="6">
-        <v>0.31590314407941189</v>
+        <v>0.31796637634190805</v>
       </c>
       <c r="E2" s="6">
         <v>0.12703422713847223</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3655737704918034</v>
+        <v>1.3659121171770972</v>
       </c>
       <c r="C3" s="5">
         <v>1.3814776808619806</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17232449738688263</v>
+        <v>0.17176707378436484</v>
       </c>
       <c r="E3" s="6">
         <v>0.17001046755059315</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3296762833536502</v>
+        <v>1.3281664016958132</v>
       </c>
       <c r="C4" s="5">
         <v>1.3202993934701253</v>
       </c>
       <c r="D4" s="6">
-        <v>0.21097902497571011</v>
+        <v>0.21022727272727273</v>
       </c>
       <c r="E4" s="6">
         <v>0.20542933644389066</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.300588427590716</v>
+        <v>1.3012924071082392</v>
       </c>
       <c r="C5" s="5">
         <v>1.3376422649992976</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3478877851762903E-2</v>
+        <v>8.3534635160119303E-2</v>
       </c>
       <c r="E5" s="6">
         <v>9.9617877188807866E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2459742945782242</v>
+        <v>1.2466906474820143</v>
       </c>
       <c r="C6" s="5">
         <v>1.2508368200836821</v>
       </c>
       <c r="D6" s="6">
-        <v>0.22639174568136591</v>
+        <v>0.23244535861803708</v>
       </c>
       <c r="E6" s="6">
         <v>0.13768735177486102</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.2342102460325912</v>
+        <v>1.2337876910367618</v>
       </c>
       <c r="C7" s="5">
         <v>1.225040749796251</v>
       </c>
       <c r="D7" s="6">
-        <v>9.7698278911989345E-2</v>
+        <v>9.7843878190231784E-2</v>
       </c>
       <c r="E7" s="6">
         <v>0.10101779337456648</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="5">
-        <v>1.2280732652342374</v>
+        <v>1.2275168357343789</v>
       </c>
       <c r="C8" s="5">
         <v>1.2349717561757021</v>
       </c>
       <c r="D8" s="6">
-        <v>0.11028669101079948</v>
+        <v>0.11041564700124243</v>
       </c>
       <c r="E8" s="6">
         <v>0.10856154353079008</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>1.2280701754385965</v>
+        <v>1.226970402394413</v>
       </c>
       <c r="C9" s="5">
         <v>1.1993172005221406</v>
       </c>
       <c r="D9" s="6">
-        <v>9.9462891871877152E-2</v>
+        <v>9.9396744070737952E-2</v>
       </c>
       <c r="E9" s="6">
         <v>8.9892407119904677E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>1.2245256500351371</v>
+        <v>1.2243993866075991</v>
       </c>
       <c r="C10" s="5">
         <v>1.3068905616676318</v>
       </c>
       <c r="D10" s="6">
-        <v>6.9782267555904276E-2</v>
+        <v>6.9585734272367264E-2</v>
       </c>
       <c r="E10" s="6">
         <v>7.4165530420965617E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2122936824132045</v>
+        <v>1.2110682110682112</v>
       </c>
       <c r="C11" s="5">
         <v>1.2055681450307543</v>
       </c>
       <c r="D11" s="6">
-        <v>9.2140684543579349E-2</v>
+        <v>9.2081873127126818E-2</v>
       </c>
       <c r="E11" s="6">
         <v>9.4505292785902223E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.206989247311828</v>
+        <v>1.2059302704463994</v>
       </c>
       <c r="C12" s="5">
         <v>1.3231753197893152</v>
       </c>
       <c r="D12" s="6">
-        <v>8.8047337278106513E-2</v>
+        <v>8.8303841173931807E-2</v>
       </c>
       <c r="E12" s="6">
         <v>8.7064758098856831E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>1.2012628255722178</v>
+        <v>1.2011010857929345</v>
       </c>
       <c r="C13" s="5">
         <v>1.2062227566511348</v>
       </c>
       <c r="D13" s="6">
-        <v>9.8171393150472644E-2</v>
+        <v>9.8498199948785156E-2</v>
       </c>
       <c r="E13" s="6">
         <v>0.10362605526307592</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>1.2005710206995002</v>
+        <v>1.1987847222222223</v>
       </c>
       <c r="C14" s="5">
         <v>1.2073467966573816</v>
       </c>
       <c r="D14" s="6">
-        <v>8.0651660814000339E-2</v>
+        <v>8.0332487238849684E-2</v>
       </c>
       <c r="E14" s="6">
         <v>8.1383981070856773E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <v>1.1977827050997782</v>
+        <v>1.1959430297798879</v>
       </c>
       <c r="C15" s="5">
         <v>1.2418664383561644</v>
       </c>
       <c r="D15" s="6">
-        <v>8.4182625900623434E-2</v>
+        <v>8.4196373414731643E-2</v>
       </c>
       <c r="E15" s="6">
         <v>8.2576266393297751E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1932499999999999</v>
+        <v>1.1933153770812928</v>
       </c>
       <c r="C16" s="5">
         <v>1.2172688303735455</v>
       </c>
       <c r="D16" s="6">
-        <v>9.2453484340691089E-2</v>
+        <v>9.3043389112283145E-2</v>
       </c>
       <c r="E16" s="6">
         <v>8.3293378354943021E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>1.1905177682703223</v>
+        <v>1.190019519646949</v>
       </c>
       <c r="C17" s="5">
         <v>1.2026913372582002</v>
       </c>
       <c r="D17" s="6">
-        <v>0.12309230041700701</v>
+        <v>0.12283554860568152</v>
       </c>
       <c r="E17" s="6">
         <v>0.12134758070277497</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1877828054298643</v>
+        <v>1.1878663076191984</v>
       </c>
       <c r="C18" s="5">
         <v>1.1921855146124523</v>
       </c>
       <c r="D18" s="6">
-        <v>0.11060665641868946</v>
+        <v>0.11049075889106692</v>
       </c>
       <c r="E18" s="6">
         <v>9.9966656610723875E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="5">
-        <v>1.18021978021978</v>
+        <v>1.1808030411023995</v>
       </c>
       <c r="C19" s="5">
         <v>1.1960830580462483</v>
       </c>
       <c r="D19" s="6">
-        <v>8.720187393526406E-2</v>
+        <v>8.7155488373056131E-2</v>
       </c>
       <c r="E19" s="6">
         <v>9.2038396386222479E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="5">
-        <v>1.1781814001609381</v>
+        <v>1.1790679568457345</v>
       </c>
       <c r="C20" s="5">
         <v>1.1936572199730096</v>
       </c>
       <c r="D20" s="6">
-        <v>8.6279060541140998E-2</v>
+        <v>8.6470214853142005E-2</v>
       </c>
       <c r="E20" s="6">
         <v>8.5774643811434695E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="8">
-        <v>1.2367901648179573</v>
+        <v>1.2364569015601308</v>
       </c>
       <c r="C21" s="8">
         <v>1.2499860599977697</v>
       </c>
       <c r="D21" s="9">
-        <v>0.11013960069852489</v>
+        <v>0.11031295013790877</v>
       </c>
       <c r="E21" s="9">
         <v>0.10371404902041577</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CDF003-4C17-4137-B69B-63FDEDCCC08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA97CA63-D3D3-4C8E-8296-754A90D95323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\ %;\-0.00\ %;0.00\ %"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -137,7 +137,6 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -537,9 +536,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17233115-4901-4354-B5A2-D6FF1650C878}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="19.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" style="3" bestFit="1" customWidth="1"/>
@@ -547,7 +546,7 @@
     <col min="6" max="16384" width="10.90625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,341 +563,341 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="14.5">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4051471525035035</v>
+        <v>1.4051891367604268</v>
       </c>
       <c r="C2" s="5">
         <v>1.4093913836334626</v>
       </c>
       <c r="D2" s="6">
-        <v>0.31796637634190805</v>
+        <v>0.31914564308930504</v>
       </c>
       <c r="E2" s="6">
         <v>0.12703422713847223</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.5">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3659121171770972</v>
+        <v>1.3668277791910455</v>
       </c>
       <c r="C3" s="5">
         <v>1.3814776808619806</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17176707378436484</v>
+        <v>0.17166688501681296</v>
       </c>
       <c r="E3" s="6">
         <v>0.17001046755059315</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="14.5">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3281664016958132</v>
+        <v>1.3261336364784639</v>
       </c>
       <c r="C4" s="5">
         <v>1.3202993934701253</v>
       </c>
       <c r="D4" s="6">
-        <v>0.21022727272727273</v>
+        <v>0.21034033847870559</v>
       </c>
       <c r="E4" s="6">
         <v>0.20542933644389066</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="14.5">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.3012924071082392</v>
+        <v>1.3003321208287206</v>
       </c>
       <c r="C5" s="5">
         <v>1.3376422649992976</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3534635160119303E-2</v>
+        <v>8.3434498047081182E-2</v>
       </c>
       <c r="E5" s="6">
         <v>9.9617877188807866E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="14.5">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2466906474820143</v>
+        <v>1.2450103234686856</v>
       </c>
       <c r="C6" s="5">
         <v>1.2508368200836821</v>
       </c>
       <c r="D6" s="6">
-        <v>0.23244535861803708</v>
+        <v>0.24298065185036538</v>
       </c>
       <c r="E6" s="6">
         <v>0.13768735177486102</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="14.5">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.2337876910367618</v>
+        <v>1.2321727981063222</v>
       </c>
       <c r="C7" s="5">
         <v>1.225040749796251</v>
       </c>
       <c r="D7" s="6">
-        <v>9.7843878190231784E-2</v>
+        <v>9.782996748328332E-2</v>
       </c>
       <c r="E7" s="6">
         <v>0.10101779337456648</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="14.5">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="5">
-        <v>1.2275168357343789</v>
+        <v>1.2269330734243016</v>
       </c>
       <c r="C8" s="5">
         <v>1.2349717561757021</v>
       </c>
       <c r="D8" s="6">
-        <v>0.11041564700124243</v>
+        <v>0.11074432201484147</v>
       </c>
       <c r="E8" s="6">
         <v>0.10856154353079008</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="14.5">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>1.226970402394413</v>
+        <v>1.2261458748505381</v>
       </c>
       <c r="C9" s="5">
         <v>1.1993172005221406</v>
       </c>
       <c r="D9" s="6">
-        <v>9.9396744070737952E-2</v>
+        <v>9.9434858080419769E-2</v>
       </c>
       <c r="E9" s="6">
         <v>8.9892407119904677E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="14.5">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>1.2243993866075991</v>
+        <v>1.2235924062956351</v>
       </c>
       <c r="C10" s="5">
         <v>1.3068905616676318</v>
       </c>
       <c r="D10" s="6">
-        <v>6.9585734272367264E-2</v>
+        <v>6.962268413917759E-2</v>
       </c>
       <c r="E10" s="6">
         <v>7.4165530420965617E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="14.5">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2110682110682112</v>
+        <v>1.2146477888481035</v>
       </c>
       <c r="C11" s="5">
         <v>1.2055681450307543</v>
       </c>
       <c r="D11" s="6">
-        <v>9.2081873127126818E-2</v>
+        <v>9.2266752681235381E-2</v>
       </c>
       <c r="E11" s="6">
         <v>9.4505292785902223E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="14.5">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.2059302704463994</v>
+        <v>1.2088390911920324</v>
       </c>
       <c r="C12" s="5">
         <v>1.3231753197893152</v>
       </c>
       <c r="D12" s="6">
-        <v>8.8303841173931807E-2</v>
+        <v>8.8490456911509544E-2</v>
       </c>
       <c r="E12" s="6">
         <v>8.7064758098856831E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="14.5">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>1.2011010857929345</v>
+        <v>1.2005579210101307</v>
       </c>
       <c r="C13" s="5">
         <v>1.2062227566511348</v>
       </c>
       <c r="D13" s="6">
-        <v>9.8498199948785156E-2</v>
+        <v>9.8056435358479702E-2</v>
       </c>
       <c r="E13" s="6">
         <v>0.10362605526307592</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="14.5">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>1.1987847222222223</v>
+        <v>1.1973509933774835</v>
       </c>
       <c r="C14" s="5">
         <v>1.2073467966573816</v>
       </c>
       <c r="D14" s="6">
-        <v>8.0332487238849684E-2</v>
+        <v>8.035013502547525E-2</v>
       </c>
       <c r="E14" s="6">
         <v>8.1383981070856773E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="14.5">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <v>1.1959430297798879</v>
+        <v>1.1919900908340213</v>
       </c>
       <c r="C15" s="5">
         <v>1.2418664383561644</v>
       </c>
       <c r="D15" s="6">
-        <v>8.4196373414731643E-2</v>
+        <v>8.4457927956201828E-2</v>
       </c>
       <c r="E15" s="6">
         <v>8.2576266393297751E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="14.5">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1933153770812928</v>
+        <v>1.1917310845631297</v>
       </c>
       <c r="C16" s="5">
         <v>1.2172688303735455</v>
       </c>
       <c r="D16" s="6">
-        <v>9.3043389112283145E-2</v>
+        <v>9.4099235126854322E-2</v>
       </c>
       <c r="E16" s="6">
         <v>8.3293378354943021E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="14.5">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>1.190019519646949</v>
+        <v>1.1901676520612294</v>
       </c>
       <c r="C17" s="5">
         <v>1.2026913372582002</v>
       </c>
       <c r="D17" s="6">
-        <v>0.12283554860568152</v>
+        <v>0.12278363945544407</v>
       </c>
       <c r="E17" s="6">
         <v>0.12134758070277497</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="14.5">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1878663076191984</v>
+        <v>1.1886477462437397</v>
       </c>
       <c r="C18" s="5">
         <v>1.1921855146124523</v>
       </c>
       <c r="D18" s="6">
-        <v>0.11049075889106692</v>
+        <v>0.11039994638339226</v>
       </c>
       <c r="E18" s="6">
         <v>9.9966656610723875E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="14.5">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="5">
-        <v>1.1808030411023995</v>
+        <v>1.1793772563176896</v>
       </c>
       <c r="C19" s="5">
         <v>1.1960830580462483</v>
       </c>
       <c r="D19" s="6">
-        <v>8.7155488373056131E-2</v>
+        <v>8.7592394956322386E-2</v>
       </c>
       <c r="E19" s="6">
         <v>9.2038396386222479E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="14.5">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="5">
-        <v>1.1790679568457345</v>
+        <v>1.17815663292488</v>
       </c>
       <c r="C20" s="5">
         <v>1.1936572199730096</v>
       </c>
       <c r="D20" s="6">
-        <v>8.6470214853142005E-2</v>
+        <v>8.6389410508487058E-2</v>
       </c>
       <c r="E20" s="6">
         <v>8.5774643811434695E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="14.5">
       <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="8">
-        <v>1.2364569015601308</v>
+        <v>1.235796647832744</v>
       </c>
       <c r="C21" s="8">
         <v>1.2499860599977697</v>
       </c>
       <c r="D21" s="9">
-        <v>0.11031295013790877</v>
+        <v>0.11070776587909344</v>
       </c>
       <c r="E21" s="9">
         <v>0.10371404902041577</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA97CA63-D3D3-4C8E-8296-754A90D95323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00C3C78-492C-4A51-A7C0-46FFF90660AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\ %;\-0.00\ %;0.00\ %"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -134,9 +134,15 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="9"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -183,22 +189,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -536,7 +538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17233115-4901-4354-B5A2-D6FF1650C878}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
@@ -546,7 +548,7 @@
     <col min="6" max="16384" width="10.90625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,341 +565,341 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1.4051891367604268</v>
+        <v>1.4023941068139965</v>
       </c>
       <c r="C2" s="5">
         <v>1.4093913836334626</v>
       </c>
       <c r="D2" s="6">
-        <v>0.31914564308930504</v>
+        <v>0.31954099084188459</v>
       </c>
       <c r="E2" s="6">
         <v>0.12703422713847223</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.3668277791910455</v>
+        <v>1.3613908872901679</v>
       </c>
       <c r="C3" s="5">
         <v>1.3814776808619806</v>
       </c>
       <c r="D3" s="6">
-        <v>0.17166688501681296</v>
+        <v>0.17192331478045764</v>
       </c>
       <c r="E3" s="6">
         <v>0.17001046755059315</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>1.3261336364784639</v>
+        <v>1.3209285628814167</v>
       </c>
       <c r="C4" s="5">
         <v>1.3202993934701253</v>
       </c>
       <c r="D4" s="6">
-        <v>0.21034033847870559</v>
+        <v>0.21092882382635034</v>
       </c>
       <c r="E4" s="6">
         <v>0.20542933644389066</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>1.3003321208287206</v>
+        <v>1.2987833050977977</v>
       </c>
       <c r="C5" s="5">
         <v>1.3376422649992976</v>
       </c>
       <c r="D5" s="6">
-        <v>8.3434498047081182E-2</v>
+        <v>8.3209452532294448E-2</v>
       </c>
       <c r="E5" s="6">
         <v>9.9617877188807866E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1.2450103234686856</v>
+        <v>1.2439264609323704</v>
       </c>
       <c r="C6" s="5">
         <v>1.2508368200836821</v>
       </c>
       <c r="D6" s="6">
-        <v>0.24298065185036538</v>
+        <v>0.25468653321961904</v>
       </c>
       <c r="E6" s="6">
         <v>0.13768735177486102</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>1.2321727981063222</v>
+        <v>1.2303013288414748</v>
       </c>
       <c r="C7" s="5">
         <v>1.225040749796251</v>
       </c>
       <c r="D7" s="6">
-        <v>9.782996748328332E-2</v>
+        <v>9.8107802903021457E-2</v>
       </c>
       <c r="E7" s="6">
         <v>0.10101779337456648</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1.2249032551786934</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.1993172005221406</v>
+      </c>
+      <c r="D8" s="6">
+        <v>9.9999241222845259E-2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>8.9892407119904677E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
-        <v>1.2269330734243016</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B9" s="5">
+        <v>1.2236048848353689</v>
+      </c>
+      <c r="C9" s="5">
         <v>1.2349717561757021</v>
       </c>
-      <c r="D8" s="6">
-        <v>0.11074432201484147</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D9" s="6">
+        <v>0.11126782366397771</v>
+      </c>
+      <c r="E9" s="6">
         <v>0.10856154353079008</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.5">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5">
-        <v>1.2261458748505381</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.1993172005221406</v>
-      </c>
-      <c r="D9" s="6">
-        <v>9.9434858080419769E-2</v>
-      </c>
-      <c r="E9" s="6">
-        <v>8.9892407119904677E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>1.2235924062956351</v>
+        <v>1.2216407572725874</v>
       </c>
       <c r="C10" s="5">
         <v>1.3068905616676318</v>
       </c>
       <c r="D10" s="6">
-        <v>6.962268413917759E-2</v>
+        <v>6.9743226415904511E-2</v>
       </c>
       <c r="E10" s="6">
         <v>7.4165530420965617E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>1.2146477888481035</v>
+        <v>1.2150662251655631</v>
       </c>
       <c r="C11" s="5">
         <v>1.2055681450307543</v>
       </c>
       <c r="D11" s="6">
-        <v>9.2266752681235381E-2</v>
+        <v>9.2837380879188441E-2</v>
       </c>
       <c r="E11" s="6">
         <v>9.4505292785902223E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>1.2088390911920324</v>
+        <v>1.2089418777943366</v>
       </c>
       <c r="C12" s="5">
         <v>1.3231753197893152</v>
       </c>
       <c r="D12" s="6">
-        <v>8.8490456911509544E-2</v>
+        <v>8.8475738396624468E-2</v>
       </c>
       <c r="E12" s="6">
         <v>8.7064758098856831E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>1.2005579210101307</v>
+        <v>1.2005325112107623</v>
       </c>
       <c r="C13" s="5">
         <v>1.2062227566511348</v>
       </c>
       <c r="D13" s="6">
-        <v>9.8056435358479702E-2</v>
+        <v>9.7949323304142535E-2</v>
       </c>
       <c r="E13" s="6">
         <v>0.10362605526307592</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>1.1973509933774835</v>
+        <v>1.1960414703110274</v>
       </c>
       <c r="C14" s="5">
         <v>1.2073467966573816</v>
       </c>
       <c r="D14" s="6">
-        <v>8.035013502547525E-2</v>
+        <v>8.0634333557106488E-2</v>
       </c>
       <c r="E14" s="6">
         <v>8.1383981070856773E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <v>1.1919900908340213</v>
+        <v>1.193280632411067</v>
       </c>
       <c r="C15" s="5">
         <v>1.2418664383561644</v>
       </c>
       <c r="D15" s="6">
-        <v>8.4457927956201828E-2</v>
+        <v>8.4697532724046731E-2</v>
       </c>
       <c r="E15" s="6">
         <v>8.2576266393297751E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="5">
-        <v>1.1917310845631297</v>
+        <v>1.1898437499999999</v>
       </c>
       <c r="C16" s="5">
         <v>1.2172688303735455</v>
       </c>
       <c r="D16" s="6">
-        <v>9.4099235126854322E-2</v>
+        <v>9.5892463451700591E-2</v>
       </c>
       <c r="E16" s="6">
         <v>8.3293378354943021E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="14.5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>1.1901676520612294</v>
+        <v>1.1897285172867198</v>
       </c>
       <c r="C17" s="5">
         <v>1.2026913372582002</v>
       </c>
       <c r="D17" s="6">
-        <v>0.12278363945544407</v>
+        <v>0.12237461074670376</v>
       </c>
       <c r="E17" s="6">
         <v>0.12134758070277497</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="14.5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>1.1886477462437397</v>
+        <v>1.1874728142670727</v>
       </c>
       <c r="C18" s="5">
         <v>1.1921855146124523</v>
       </c>
       <c r="D18" s="6">
-        <v>0.11039994638339226</v>
+        <v>0.11036965914546328</v>
       </c>
       <c r="E18" s="6">
         <v>9.9966656610723875E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="14.5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="5">
-        <v>1.1793772563176896</v>
+        <v>1.1770498822521944</v>
       </c>
       <c r="C19" s="5">
         <v>1.1960830580462483</v>
       </c>
       <c r="D19" s="6">
-        <v>8.7592394956322386E-2</v>
+        <v>8.7708427219468227E-2</v>
       </c>
       <c r="E19" s="6">
         <v>9.2038396386222479E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="14.5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="5">
-        <v>1.17815663292488</v>
+        <v>1.176999285057706</v>
       </c>
       <c r="C20" s="5">
         <v>1.1936572199730096</v>
       </c>
       <c r="D20" s="6">
-        <v>8.6389410508487058E-2</v>
+        <v>8.6223294643957935E-2</v>
       </c>
       <c r="E20" s="6">
         <v>8.5774643811434695E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="14.5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="8">
-        <v>1.235796647832744</v>
+        <v>1.2341507814063375</v>
       </c>
       <c r="C21" s="8">
         <v>1.2499860599977697</v>
       </c>
       <c r="D21" s="9">
-        <v>0.11070776587909344</v>
+        <v>0.11128135945819362</v>
       </c>
       <c r="E21" s="9">
         <v>0.10371404902041577</v>
